--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/59.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/59.xlsx
@@ -426,13 +426,13 @@
         <v>-20.62865978453249</v>
       </c>
       <c r="E2">
-        <v>-17.54140389486534</v>
+        <v>-18.48069091658831</v>
       </c>
       <c r="F2">
-        <v>-0.1107603243084268</v>
+        <v>-0.1833543016527615</v>
       </c>
       <c r="G2">
-        <v>-10.46577111742453</v>
+        <v>-9.767504231190369</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.73471870096843</v>
       </c>
       <c r="E3">
-        <v>-18.56449485657426</v>
+        <v>-18.30427515467149</v>
       </c>
       <c r="F3">
-        <v>0.4027777633830987</v>
+        <v>-0.1043620144892035</v>
       </c>
       <c r="G3">
-        <v>-10.75455000481515</v>
+        <v>-9.806869928197843</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.80658621882225</v>
       </c>
       <c r="E4">
-        <v>-18.68314087557522</v>
+        <v>-18.60266989245892</v>
       </c>
       <c r="F4">
-        <v>0.5840841935686321</v>
+        <v>-0.2420283931604533</v>
       </c>
       <c r="G4">
-        <v>-8.964650590279556</v>
+        <v>-9.661103297558192</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.82088135847327</v>
       </c>
       <c r="E5">
-        <v>-19.75315135647761</v>
+        <v>-18.42882177530445</v>
       </c>
       <c r="F5">
-        <v>0.5221703571485914</v>
+        <v>-0.06365604031563576</v>
       </c>
       <c r="G5">
-        <v>-10.42852085901665</v>
+        <v>-8.336736107300451</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.75775057222732</v>
       </c>
       <c r="E6">
-        <v>-18.49722890366432</v>
+        <v>-19.08644224222433</v>
       </c>
       <c r="F6">
-        <v>0.790223421755289</v>
+        <v>0.1936116807066123</v>
       </c>
       <c r="G6">
-        <v>-9.119610605881762</v>
+        <v>-8.778733663339626</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.6115890141206</v>
       </c>
       <c r="E7">
-        <v>-19.19264401465222</v>
+        <v>-20.3377456515498</v>
       </c>
       <c r="F7">
-        <v>0.7762306395871997</v>
+        <v>0.3238360066311114</v>
       </c>
       <c r="G7">
-        <v>-9.109728627447037</v>
+        <v>-8.44367003876445</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.39286285230262</v>
       </c>
       <c r="E8">
-        <v>-20.92068252513518</v>
+        <v>-20.60596263855011</v>
       </c>
       <c r="F8">
-        <v>0.9224805612862581</v>
+        <v>-0.02716728458972034</v>
       </c>
       <c r="G8">
-        <v>-8.207058727981659</v>
+        <v>-7.521577168620167</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.10645073113222</v>
       </c>
       <c r="E9">
-        <v>-21.6582622576085</v>
+        <v>-21.85766455358825</v>
       </c>
       <c r="F9">
-        <v>1.580515745252518</v>
+        <v>0.5442819682315186</v>
       </c>
       <c r="G9">
-        <v>-8.629931262440465</v>
+        <v>-7.250089260581155</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.77040160131</v>
       </c>
       <c r="E10">
-        <v>-20.23102763308504</v>
+        <v>-22.53665941782433</v>
       </c>
       <c r="F10">
-        <v>1.048751917964598</v>
+        <v>0.4184587583180933</v>
       </c>
       <c r="G10">
-        <v>-5.371420877955542</v>
+        <v>-6.851731315840653</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.41590797507894</v>
       </c>
       <c r="E11">
-        <v>-20.50898536767584</v>
+        <v>-22.93200425564197</v>
       </c>
       <c r="F11">
-        <v>1.259480301562764</v>
+        <v>0.5072042432822127</v>
       </c>
       <c r="G11">
-        <v>-7.65370104109248</v>
+        <v>-5.645080503868316</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.0801159524347</v>
       </c>
       <c r="E12">
-        <v>-22.39767149358091</v>
+        <v>-22.81445865582487</v>
       </c>
       <c r="F12">
-        <v>2.002817447199706</v>
+        <v>1.02971437831346</v>
       </c>
       <c r="G12">
-        <v>-8.048920588661753</v>
+        <v>-5.64883466250985</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.78670988559803</v>
       </c>
       <c r="E13">
-        <v>-24.57882911327137</v>
+        <v>-23.9022615111034</v>
       </c>
       <c r="F13">
-        <v>1.613201466232181</v>
+        <v>0.9658870131929522</v>
       </c>
       <c r="G13">
-        <v>-7.021820524557328</v>
+        <v>-4.783563996001618</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.56870349367644</v>
       </c>
       <c r="E14">
-        <v>-23.0451391217756</v>
+        <v>-25.33997502448061</v>
       </c>
       <c r="F14">
-        <v>2.38746488048524</v>
+        <v>1.320050526055464</v>
       </c>
       <c r="G14">
-        <v>-6.226276568197227</v>
+        <v>-5.048301701686056</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.45650675567648</v>
       </c>
       <c r="E15">
-        <v>-26.47718805965683</v>
+        <v>-25.1426060133303</v>
       </c>
       <c r="F15">
-        <v>2.793091546614074</v>
+        <v>1.667113273541178</v>
       </c>
       <c r="G15">
-        <v>-5.628355627803918</v>
+        <v>-4.576108659783189</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.45426865750977</v>
       </c>
       <c r="E16">
-        <v>-26.05510258282389</v>
+        <v>-27.27547198620296</v>
       </c>
       <c r="F16">
-        <v>3.229475494408853</v>
+        <v>1.969765587828006</v>
       </c>
       <c r="G16">
-        <v>-5.770056908521343</v>
+        <v>-3.649841191713886</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.55557033668625</v>
       </c>
       <c r="E17">
-        <v>-27.51271873946481</v>
+        <v>-27.99226149450707</v>
       </c>
       <c r="F17">
-        <v>3.239715772242261</v>
+        <v>2.291911043837511</v>
       </c>
       <c r="G17">
-        <v>-5.751547648411277</v>
+        <v>-4.742936981143682</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.74911132509318</v>
       </c>
       <c r="E18">
-        <v>-27.22208127765253</v>
+        <v>-28.83354781023004</v>
       </c>
       <c r="F18">
-        <v>3.596644375495317</v>
+        <v>2.67177548373928</v>
       </c>
       <c r="G18">
-        <v>-5.738643141899198</v>
+        <v>-4.070724088303589</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-19.01469211886162</v>
       </c>
       <c r="E19">
-        <v>-29.00081605465136</v>
+        <v>-30.26310101344543</v>
       </c>
       <c r="F19">
-        <v>3.622767769910002</v>
+        <v>2.664323490583696</v>
       </c>
       <c r="G19">
-        <v>-4.614179933484808</v>
+        <v>-3.75506688167962</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-19.31374554011707</v>
       </c>
       <c r="E20">
-        <v>-30.05179335929951</v>
+        <v>-30.69315207605785</v>
       </c>
       <c r="F20">
-        <v>4.082150510276108</v>
+        <v>3.005183422957248</v>
       </c>
       <c r="G20">
-        <v>-4.739881347610934</v>
+        <v>-4.720087595831632</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.6178681554236</v>
       </c>
       <c r="E21">
-        <v>-30.06523839862828</v>
+        <v>-31.15275369580733</v>
       </c>
       <c r="F21">
-        <v>4.424703625620982</v>
+        <v>3.270709966985407</v>
       </c>
       <c r="G21">
-        <v>-5.197968154970967</v>
+        <v>-3.591386889126974</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-19.90490067723753</v>
       </c>
       <c r="E22">
-        <v>-30.1970237849625</v>
+        <v>-31.53927933049503</v>
       </c>
       <c r="F22">
-        <v>4.190775984540013</v>
+        <v>3.16644833219945</v>
       </c>
       <c r="G22">
-        <v>-4.758688556819534</v>
+        <v>-3.2647618451314</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-20.1422508184382</v>
       </c>
       <c r="E23">
-        <v>-32.53811125694485</v>
+        <v>-31.80793784371108</v>
       </c>
       <c r="F23">
-        <v>4.32817231543795</v>
+        <v>2.952711318194316</v>
       </c>
       <c r="G23">
-        <v>-5.520994635965353</v>
+        <v>-4.284595261777126</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-20.30588885740633</v>
       </c>
       <c r="E24">
-        <v>-31.16324390584609</v>
+        <v>-32.99493012941662</v>
       </c>
       <c r="F24">
-        <v>4.450760750643442</v>
+        <v>3.304605104373157</v>
       </c>
       <c r="G24">
-        <v>-4.76043321431873</v>
+        <v>-3.745992676356478</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-20.3845733058913</v>
       </c>
       <c r="E25">
-        <v>-30.68827490955159</v>
+        <v>-31.82491962123985</v>
       </c>
       <c r="F25">
-        <v>4.538812892091419</v>
+        <v>3.608688837532022</v>
       </c>
       <c r="G25">
-        <v>-4.508497388234654</v>
+        <v>-3.900270719577594</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-20.37293882372741</v>
       </c>
       <c r="E26">
-        <v>-32.21723264570934</v>
+        <v>-32.54282992686085</v>
       </c>
       <c r="F26">
-        <v>3.832483888541948</v>
+        <v>3.262711251343975</v>
       </c>
       <c r="G26">
-        <v>-4.626094586880645</v>
+        <v>-3.874071062179802</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-20.26268640640232</v>
       </c>
       <c r="E27">
-        <v>-33.78470958177635</v>
+        <v>-33.3503315622496</v>
       </c>
       <c r="F27">
-        <v>3.700475259231819</v>
+        <v>3.053056431899837</v>
       </c>
       <c r="G27">
-        <v>-5.047427717663688</v>
+        <v>-3.042558028535518</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-20.06327004299103</v>
       </c>
       <c r="E28">
-        <v>-31.28857168824538</v>
+        <v>-33.03531732485403</v>
       </c>
       <c r="F28">
-        <v>3.977902129368595</v>
+        <v>3.092832977847463</v>
       </c>
       <c r="G28">
-        <v>-4.606218071462861</v>
+        <v>-3.835814397927984</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-19.79477921611796</v>
       </c>
       <c r="E29">
-        <v>-31.24972870244458</v>
+        <v>-32.37881765525104</v>
       </c>
       <c r="F29">
-        <v>3.662642063211159</v>
+        <v>2.620077074130563</v>
       </c>
       <c r="G29">
-        <v>-3.809833236535784</v>
+        <v>-2.709921033840628</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-19.46957907598265</v>
       </c>
       <c r="E30">
-        <v>-30.02187826000484</v>
+        <v>-33.09554150068203</v>
       </c>
       <c r="F30">
-        <v>3.385861319648567</v>
+        <v>2.887258696229516</v>
       </c>
       <c r="G30">
-        <v>-3.29387809314929</v>
+        <v>-2.833606325733339</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-19.1075799742412</v>
       </c>
       <c r="E31">
-        <v>-31.34661540383869</v>
+        <v>-32.14096861494617</v>
       </c>
       <c r="F31">
-        <v>3.61259707493843</v>
+        <v>2.23140543200223</v>
       </c>
       <c r="G31">
-        <v>-4.929929835383875</v>
+        <v>-3.447007377068279</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-18.73572876638109</v>
       </c>
       <c r="E32">
-        <v>-31.34019402769582</v>
+        <v>-31.97389962338119</v>
       </c>
       <c r="F32">
-        <v>3.29690957120115</v>
+        <v>2.267550415255983</v>
       </c>
       <c r="G32">
-        <v>-5.264460462127229</v>
+        <v>-3.14734341594453</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-18.37647170413592</v>
       </c>
       <c r="E33">
-        <v>-30.21309986768973</v>
+        <v>-31.98266674906004</v>
       </c>
       <c r="F33">
-        <v>3.298299571703047</v>
+        <v>2.49558008042902</v>
       </c>
       <c r="G33">
-        <v>-4.478046990364437</v>
+        <v>-2.910887700802085</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-18.03973266880209</v>
       </c>
       <c r="E34">
-        <v>-29.95487495858735</v>
+        <v>-30.60204370749753</v>
       </c>
       <c r="F34">
-        <v>3.304313519047372</v>
+        <v>2.422231460380735</v>
       </c>
       <c r="G34">
-        <v>-3.51400288714651</v>
+        <v>-2.717184370753789</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-17.74288279544936</v>
       </c>
       <c r="E35">
-        <v>-30.10842419100243</v>
+        <v>-31.0351899820942</v>
       </c>
       <c r="F35">
-        <v>2.152821529968252</v>
+        <v>2.466829104612655</v>
       </c>
       <c r="G35">
-        <v>-3.749680624087226</v>
+        <v>-2.923845176042793</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.50105509463248</v>
       </c>
       <c r="E36">
-        <v>-29.16822015329291</v>
+        <v>-30.92252154878336</v>
       </c>
       <c r="F36">
-        <v>3.367511324941752</v>
+        <v>2.669895089734926</v>
       </c>
       <c r="G36">
-        <v>-4.682188470498056</v>
+        <v>-3.373380844274888</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.31159437111562</v>
       </c>
       <c r="E37">
-        <v>-28.93736307685588</v>
+        <v>-30.10895628669834</v>
       </c>
       <c r="F37">
-        <v>3.440298311890939</v>
+        <v>2.612035283384186</v>
       </c>
       <c r="G37">
-        <v>-3.848834773533937</v>
+        <v>-2.740758765538939</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.17376796422237</v>
       </c>
       <c r="E38">
-        <v>-27.0038586436969</v>
+        <v>-29.3616856198486</v>
       </c>
       <c r="F38">
-        <v>3.006638036116564</v>
+        <v>2.334142870767036</v>
       </c>
       <c r="G38">
-        <v>-4.101823353099502</v>
+        <v>-2.311566399645665</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.08854617499292</v>
       </c>
       <c r="E39">
-        <v>-28.65612219860952</v>
+        <v>-28.39052266958564</v>
       </c>
       <c r="F39">
-        <v>3.80198340077087</v>
+        <v>2.944878276033444</v>
       </c>
       <c r="G39">
-        <v>-2.997312802650299</v>
+        <v>-2.823750831662929</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.04852802309112</v>
       </c>
       <c r="E40">
-        <v>-26.70881044820115</v>
+        <v>-28.40394959501839</v>
       </c>
       <c r="F40">
-        <v>3.038621301538653</v>
+        <v>3.05728276238892</v>
       </c>
       <c r="G40">
-        <v>-3.439111725957118</v>
+        <v>-3.838856789278574</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.0361568209501</v>
       </c>
       <c r="E41">
-        <v>-27.03295861767019</v>
+        <v>-28.11919914941607</v>
       </c>
       <c r="F41">
-        <v>3.227237245686489</v>
+        <v>3.171138548434101</v>
       </c>
       <c r="G41">
-        <v>-3.294364743343563</v>
+        <v>-2.944257999837939</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.04284954850235</v>
       </c>
       <c r="E42">
-        <v>-26.32859977051714</v>
+        <v>-27.42498408404021</v>
       </c>
       <c r="F42">
-        <v>3.794110596974663</v>
+        <v>3.269626462422545</v>
       </c>
       <c r="G42">
-        <v>-5.699075501613829</v>
+        <v>-3.054899742305921</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.0627865321596</v>
       </c>
       <c r="E43">
-        <v>-24.99450227090944</v>
+        <v>-27.05330505138665</v>
       </c>
       <c r="F43">
-        <v>3.691013646757042</v>
+        <v>3.128192668803363</v>
       </c>
       <c r="G43">
-        <v>-3.965753310344378</v>
+        <v>-3.256899299475631</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-17.07985196960664</v>
       </c>
       <c r="E44">
-        <v>-26.40624498585266</v>
+        <v>-26.08398971851882</v>
       </c>
       <c r="F44">
-        <v>4.184788544952577</v>
+        <v>3.25388913850416</v>
       </c>
       <c r="G44">
-        <v>-4.800209418973074</v>
+        <v>-4.208575204558841</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-17.08559821066205</v>
       </c>
       <c r="E45">
-        <v>-25.42332611706579</v>
+        <v>-25.44837310680221</v>
       </c>
       <c r="F45">
-        <v>3.703318216158226</v>
+        <v>3.347458206854781</v>
       </c>
       <c r="G45">
-        <v>-2.903667400980935</v>
+        <v>-3.482453388157256</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-17.08106249125158</v>
       </c>
       <c r="E46">
-        <v>-23.28541542414858</v>
+        <v>-24.365479117348</v>
       </c>
       <c r="F46">
-        <v>4.258049358056166</v>
+        <v>3.244962651371593</v>
       </c>
       <c r="G46">
-        <v>-4.780571262834116</v>
+        <v>-4.11228136645806</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-17.0657823609985</v>
       </c>
       <c r="E47">
-        <v>-23.32249004084938</v>
+        <v>-24.60608599832354</v>
       </c>
       <c r="F47">
-        <v>4.548728449902929</v>
+        <v>3.526953825897795</v>
       </c>
       <c r="G47">
-        <v>-4.348055109219414</v>
+        <v>-3.978349936121305</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-17.0360590517639</v>
       </c>
       <c r="E48">
-        <v>-21.65775959699365</v>
+        <v>-24.17107172819871</v>
       </c>
       <c r="F48">
-        <v>4.257409858421204</v>
+        <v>3.587119807097928</v>
       </c>
       <c r="G48">
-        <v>-5.248357968624214</v>
+        <v>-4.264294996530315</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.99831086923663</v>
       </c>
       <c r="E49">
-        <v>-23.19012274560517</v>
+        <v>-23.79648994370624</v>
       </c>
       <c r="F49">
-        <v>4.290175102671536</v>
+        <v>3.488520891877509</v>
       </c>
       <c r="G49">
-        <v>-3.630249383212479</v>
+        <v>-4.320319358691401</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-16.96540321992012</v>
       </c>
       <c r="E50">
-        <v>-23.22084844174721</v>
+        <v>-23.28432859038674</v>
       </c>
       <c r="F50">
-        <v>3.961384483356773</v>
+        <v>3.369726379376837</v>
       </c>
       <c r="G50">
-        <v>-5.480473558564674</v>
+        <v>-5.152861971998397</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-16.93930689908592</v>
       </c>
       <c r="E51">
-        <v>-21.08396118395574</v>
+        <v>-21.96305120069475</v>
       </c>
       <c r="F51">
-        <v>4.140179303577018</v>
+        <v>3.343675881293599</v>
       </c>
       <c r="G51">
-        <v>-6.054763824898664</v>
+        <v>-4.681367455204316</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-16.92509611646033</v>
       </c>
       <c r="E52">
-        <v>-22.47550237635074</v>
+        <v>-22.58952029491587</v>
       </c>
       <c r="F52">
-        <v>4.279272130915889</v>
+        <v>3.627868856376442</v>
       </c>
       <c r="G52">
-        <v>-7.280562832270146</v>
+        <v>-4.589566027400326</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-16.93486086583878</v>
       </c>
       <c r="E53">
-        <v>-21.18923461921205</v>
+        <v>-20.85511474997812</v>
       </c>
       <c r="F53">
-        <v>4.643427411390968</v>
+        <v>3.859286544226928</v>
       </c>
       <c r="G53">
-        <v>-6.499896467563529</v>
+        <v>-4.697777829442484</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.97352985665476</v>
       </c>
       <c r="E54">
-        <v>-21.34154531398604</v>
+        <v>-20.92800506760558</v>
       </c>
       <c r="F54">
-        <v>4.048467434943474</v>
+        <v>3.775132699776527</v>
       </c>
       <c r="G54">
-        <v>-5.615156482738843</v>
+        <v>-5.091990971167818</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-17.03839714917711</v>
       </c>
       <c r="E55">
-        <v>-19.19846763222608</v>
+        <v>-20.74791671326855</v>
       </c>
       <c r="F55">
-        <v>4.509124204375085</v>
+        <v>3.756901989975715</v>
       </c>
       <c r="G55">
-        <v>-5.844295892239499</v>
+        <v>-4.815543865910977</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-17.13108993139318</v>
       </c>
       <c r="E56">
-        <v>-19.34931562989559</v>
+        <v>-20.21448511753502</v>
       </c>
       <c r="F56">
-        <v>5.088814056119373</v>
+        <v>3.838113473411373</v>
       </c>
       <c r="G56">
-        <v>-5.613752811430193</v>
+        <v>-5.189556058755679</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-17.25700225851955</v>
       </c>
       <c r="E57">
-        <v>-18.99199185984635</v>
+        <v>-19.93919012566072</v>
       </c>
       <c r="F57">
-        <v>4.435157622244311</v>
+        <v>3.77652435701323</v>
       </c>
       <c r="G57">
-        <v>-6.106491098949776</v>
+        <v>-5.275232977312017</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-17.407428078698</v>
       </c>
       <c r="E58">
-        <v>-19.17712040575393</v>
+        <v>-20.23209635295085</v>
       </c>
       <c r="F58">
-        <v>3.7992994903858</v>
+        <v>4.227394793948167</v>
       </c>
       <c r="G58">
-        <v>-5.231153063456621</v>
+        <v>-6.12887038679525</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-17.57472661600978</v>
       </c>
       <c r="E59">
-        <v>-18.48820818344104</v>
+        <v>-19.32445883606749</v>
       </c>
       <c r="F59">
-        <v>3.969625082279823</v>
+        <v>3.860754411264689</v>
       </c>
       <c r="G59">
-        <v>-6.700763818158809</v>
+        <v>-5.232609703493901</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-17.75975971899047</v>
       </c>
       <c r="E60">
-        <v>-16.61974622245423</v>
+        <v>-19.93830254475522</v>
       </c>
       <c r="F60">
-        <v>4.741557470661403</v>
+        <v>3.823482848343128</v>
       </c>
       <c r="G60">
-        <v>-7.509655894133251</v>
+        <v>-6.196518074344717</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-17.95645930033538</v>
       </c>
       <c r="E61">
-        <v>-18.52140189791726</v>
+        <v>-19.69416345405369</v>
       </c>
       <c r="F61">
-        <v>4.20245430818468</v>
+        <v>4.147101141594812</v>
       </c>
       <c r="G61">
-        <v>-6.963184141965757</v>
+        <v>-5.706934736724059</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-18.15350653781512</v>
       </c>
       <c r="E62">
-        <v>-16.41514523831367</v>
+        <v>-18.6912196732049</v>
       </c>
       <c r="F62">
-        <v>4.339852295817423</v>
+        <v>3.759242956256027</v>
       </c>
       <c r="G62">
-        <v>-7.954464103335268</v>
+        <v>-6.198206452569746</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-18.34553111328105</v>
       </c>
       <c r="E63">
-        <v>-17.92998772098952</v>
+        <v>-19.08421876148657</v>
       </c>
       <c r="F63">
-        <v>4.627499562969939</v>
+        <v>4.326108023870173</v>
       </c>
       <c r="G63">
-        <v>-6.900753874186181</v>
+        <v>-6.427872238811145</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-18.53338733811431</v>
       </c>
       <c r="E64">
-        <v>-18.16012024158532</v>
+        <v>-18.52677719656437</v>
       </c>
       <c r="F64">
-        <v>4.286197282403293</v>
+        <v>4.018563371702412</v>
       </c>
       <c r="G64">
-        <v>-8.206247644324538</v>
+        <v>-6.598434855539936</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-18.70551151802674</v>
       </c>
       <c r="E65">
-        <v>-18.16230749453103</v>
+        <v>-18.11288372921131</v>
       </c>
       <c r="F65">
-        <v>4.403500733578926</v>
+        <v>4.112051260047559</v>
       </c>
       <c r="G65">
-        <v>-6.494208950327061</v>
+        <v>-6.234175529853927</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.85399219365292</v>
       </c>
       <c r="E66">
-        <v>-16.5054882947667</v>
+        <v>-18.91376247136385</v>
       </c>
       <c r="F66">
-        <v>4.200244223954011</v>
+        <v>4.032625736732336</v>
       </c>
       <c r="G66">
-        <v>-7.497006299627697</v>
+        <v>-7.037307256590038</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.98151576962034</v>
       </c>
       <c r="E67">
-        <v>-18.54201098312617</v>
+        <v>-18.0024161342682</v>
       </c>
       <c r="F67">
-        <v>3.916420700732816</v>
+        <v>3.887119688960992</v>
       </c>
       <c r="G67">
-        <v>-8.018337768969966</v>
+        <v>-6.770043604659136</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-19.08352279139364</v>
       </c>
       <c r="E68">
-        <v>-17.12058186228055</v>
+        <v>-17.71392064066155</v>
       </c>
       <c r="F68">
-        <v>4.284868581089203</v>
+        <v>3.960604161263336</v>
       </c>
       <c r="G68">
-        <v>-6.741678850478661</v>
+        <v>-7.060759161190235</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-19.15230523217722</v>
       </c>
       <c r="E69">
-        <v>-15.10020771223242</v>
+        <v>-18.38624959115834</v>
       </c>
       <c r="F69">
-        <v>4.495610218565814</v>
+        <v>4.074837682844193</v>
       </c>
       <c r="G69">
-        <v>-7.448609434389091</v>
+        <v>-7.425985166173712</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-19.18776025923935</v>
       </c>
       <c r="E70">
-        <v>-16.71918698318866</v>
+        <v>-16.78248599286788</v>
       </c>
       <c r="F70">
-        <v>4.533604117862616</v>
+        <v>3.817031523010126</v>
       </c>
       <c r="G70">
-        <v>-7.59111186712702</v>
+        <v>-6.871270155613431</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-19.19503706572068</v>
       </c>
       <c r="E71">
-        <v>-16.2375747155249</v>
+        <v>-17.32982906075297</v>
       </c>
       <c r="F71">
-        <v>3.795603315034508</v>
+        <v>3.762239989519355</v>
       </c>
       <c r="G71">
-        <v>-8.179309735271488</v>
+        <v>-7.04911266198308</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-19.16766923883563</v>
       </c>
       <c r="E72">
-        <v>-17.06001352242795</v>
+        <v>-17.49200730038967</v>
       </c>
       <c r="F72">
-        <v>3.731356796008184</v>
+        <v>3.954775768217239</v>
       </c>
       <c r="G72">
-        <v>-7.237658162081192</v>
+        <v>-6.811398939535712</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-19.10547834685971</v>
       </c>
       <c r="E73">
-        <v>-16.39781929676033</v>
+        <v>-17.86079263815232</v>
       </c>
       <c r="F73">
-        <v>4.033250325754048</v>
+        <v>3.873615643560554</v>
       </c>
       <c r="G73">
-        <v>-7.817407518009441</v>
+        <v>-7.539066780704137</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-19.01759121493007</v>
       </c>
       <c r="E74">
-        <v>-17.3916019746916</v>
+        <v>-17.86613623748137</v>
       </c>
       <c r="F74">
-        <v>3.853630451600614</v>
+        <v>3.517773858339971</v>
       </c>
       <c r="G74">
-        <v>-7.276921232176948</v>
+        <v>-6.69603304858319</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.90390864479188</v>
       </c>
       <c r="E75">
-        <v>-17.37767691711802</v>
+        <v>-17.23576812713965</v>
       </c>
       <c r="F75">
-        <v>4.135777359198542</v>
+        <v>3.550187874811515</v>
       </c>
       <c r="G75">
-        <v>-6.265364179379401</v>
+        <v>-6.709506968928023</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.76262212538361</v>
       </c>
       <c r="E76">
-        <v>-16.3373460548619</v>
+        <v>-18.51158869474264</v>
       </c>
       <c r="F76">
-        <v>3.871882698953898</v>
+        <v>3.847869984681546</v>
       </c>
       <c r="G76">
-        <v>-6.785543578874004</v>
+        <v>-6.703329490951743</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.59971155081698</v>
       </c>
       <c r="E77">
-        <v>-17.01984142950591</v>
+        <v>-19.25154587606999</v>
       </c>
       <c r="F77">
-        <v>2.763720951980414</v>
+        <v>3.321068078136395</v>
       </c>
       <c r="G77">
-        <v>-7.394101302084991</v>
+        <v>-6.896238290070615</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-18.42299518341705</v>
       </c>
       <c r="E78">
-        <v>-17.63334550264307</v>
+        <v>-17.87073716707316</v>
       </c>
       <c r="F78">
-        <v>3.782783501108783</v>
+        <v>3.153807445632729</v>
       </c>
       <c r="G78">
-        <v>-6.513171755176007</v>
+        <v>-6.351388705217363</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-18.22790527149781</v>
       </c>
       <c r="E79">
-        <v>-17.89683929125338</v>
+        <v>-18.88300960437776</v>
       </c>
       <c r="F79">
-        <v>3.481893952655113</v>
+        <v>3.659131442158095</v>
       </c>
       <c r="G79">
-        <v>-7.423340040287834</v>
+        <v>-6.923503943132053</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-18.01788733231387</v>
       </c>
       <c r="E80">
-        <v>-17.13487825472276</v>
+        <v>-20.48213604528437</v>
       </c>
       <c r="F80">
-        <v>3.229006638458869</v>
+        <v>3.370195235326822</v>
       </c>
       <c r="G80">
-        <v>-7.468578645081974</v>
+        <v>-7.332584744874254</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.80346189911432</v>
       </c>
       <c r="E81">
-        <v>-18.58532583700954</v>
+        <v>-20.62637247090268</v>
       </c>
       <c r="F81">
-        <v>4.088676388675362</v>
+        <v>3.335582731768247</v>
       </c>
       <c r="G81">
-        <v>-7.788271406718315</v>
+        <v>-6.121064120413648</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.58461202212409</v>
       </c>
       <c r="E82">
-        <v>-19.537890344523</v>
+        <v>-21.32891539997865</v>
       </c>
       <c r="F82">
-        <v>3.261370952886245</v>
+        <v>3.397940573116189</v>
       </c>
       <c r="G82">
-        <v>-7.083102033034777</v>
+        <v>-5.418063154058333</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-17.36171787667198</v>
       </c>
       <c r="E83">
-        <v>-18.76823995912736</v>
+        <v>-21.61967513058914</v>
       </c>
       <c r="F83">
-        <v>3.334406450056272</v>
+        <v>3.308085904199721</v>
       </c>
       <c r="G83">
-        <v>-5.644395220941687</v>
+        <v>-5.62743860668954</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-17.14276701890881</v>
       </c>
       <c r="E84">
-        <v>-22.07392182982455</v>
+        <v>-23.25775097643572</v>
       </c>
       <c r="F84">
-        <v>3.065748677245531</v>
+        <v>2.910252518596425</v>
       </c>
       <c r="G84">
-        <v>-5.680890674966612</v>
+        <v>-5.852413349901791</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.93795717404814</v>
       </c>
       <c r="E85">
-        <v>-23.53791860634227</v>
+        <v>-23.4880510505698</v>
       </c>
       <c r="F85">
-        <v>3.18315484597911</v>
+        <v>2.903666997744168</v>
       </c>
       <c r="G85">
-        <v>-4.826488529463808</v>
+        <v>-5.193485676310794</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.74671474106416</v>
       </c>
       <c r="E86">
-        <v>-21.9715828457252</v>
+        <v>-24.48168881733283</v>
       </c>
       <c r="F86">
-        <v>3.075447202797508</v>
+        <v>2.890461164608739</v>
       </c>
       <c r="G86">
-        <v>-6.063222268751502</v>
+        <v>-6.002155945734106</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.57637163740356</v>
       </c>
       <c r="E87">
-        <v>-24.92439243632269</v>
+        <v>-25.34173660086959</v>
       </c>
       <c r="F87">
-        <v>2.538545840877425</v>
+        <v>2.720095811079381</v>
       </c>
       <c r="G87">
-        <v>-4.082595704607415</v>
+        <v>-5.314211340491396</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.44399066476152</v>
       </c>
       <c r="E88">
-        <v>-24.67599658005395</v>
+        <v>-26.66304116140562</v>
       </c>
       <c r="F88">
-        <v>2.932439511113007</v>
+        <v>2.984797301174352</v>
       </c>
       <c r="G88">
-        <v>-3.47730217929815</v>
+        <v>-4.733170871802832</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.35568221313606</v>
       </c>
       <c r="E89">
-        <v>-28.8253784431202</v>
+        <v>-27.76189349326287</v>
       </c>
       <c r="F89">
-        <v>3.563806234913539</v>
+        <v>2.379384984838333</v>
       </c>
       <c r="G89">
-        <v>-5.28862082347283</v>
+        <v>-4.862974051852116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.31680635394155</v>
       </c>
       <c r="E90">
-        <v>-28.65559236715062</v>
+        <v>-29.30628879731277</v>
       </c>
       <c r="F90">
-        <v>2.993702250754447</v>
+        <v>2.183030432413544</v>
       </c>
       <c r="G90">
-        <v>-5.316343331818687</v>
+        <v>-4.220135629581976</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.33702509150266</v>
       </c>
       <c r="E91">
-        <v>-31.09367295966625</v>
+        <v>-31.6381540319785</v>
       </c>
       <c r="F91">
-        <v>2.197506981144868</v>
+        <v>2.06633003270715</v>
       </c>
       <c r="G91">
-        <v>-3.278153001837752</v>
+        <v>-4.154374952989893</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.42743156936377</v>
       </c>
       <c r="E92">
-        <v>-32.83301454127236</v>
+        <v>-33.14555623185975</v>
       </c>
       <c r="F92">
-        <v>2.701891609035459</v>
+        <v>1.765902713264242</v>
       </c>
       <c r="G92">
-        <v>-4.673988249197281</v>
+        <v>-4.05118524853081</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.58484098883393</v>
       </c>
       <c r="E93">
-        <v>-34.35012126095205</v>
+        <v>-34.99046107105866</v>
       </c>
       <c r="F93">
-        <v>2.128152748712882</v>
+        <v>1.846574101153275</v>
       </c>
       <c r="G93">
-        <v>-4.15316329332252</v>
+        <v>-3.716260666868283</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.80653722811708</v>
       </c>
       <c r="E94">
-        <v>-34.51395692207555</v>
+        <v>-37.17838196667957</v>
       </c>
       <c r="F94">
-        <v>2.216127023624995</v>
+        <v>1.260792435528798</v>
       </c>
       <c r="G94">
-        <v>-4.078735608508625</v>
+        <v>-4.065887381270714</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.09983813877504</v>
       </c>
       <c r="E95">
-        <v>-35.75817779805302</v>
+        <v>-38.75326069351211</v>
       </c>
       <c r="F95">
-        <v>0.8950450329055385</v>
+        <v>1.251133671612156</v>
       </c>
       <c r="G95">
-        <v>-4.554242506496303</v>
+        <v>-4.551676833703367</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.46009991641347</v>
       </c>
       <c r="E96">
-        <v>-38.41895742108087</v>
+        <v>-40.96393490678457</v>
       </c>
       <c r="F96">
-        <v>1.161949980291956</v>
+        <v>0.8798809392298907</v>
       </c>
       <c r="G96">
-        <v>-4.367226478437334</v>
+        <v>-4.334415661597617</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.8701610564347</v>
       </c>
       <c r="E97">
-        <v>-42.6995744608894</v>
+        <v>-42.28365902989192</v>
       </c>
       <c r="F97">
-        <v>0.6370781697953276</v>
+        <v>0.4978619157134399</v>
       </c>
       <c r="G97">
-        <v>-3.774767938183823</v>
+        <v>-4.120749741947516</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.33198259829854</v>
       </c>
       <c r="E98">
-        <v>-44.66342193413678</v>
+        <v>-45.30594673295209</v>
       </c>
       <c r="F98">
-        <v>0.23033486440752</v>
+        <v>0.1271898688805367</v>
       </c>
       <c r="G98">
-        <v>-4.762254014365329</v>
+        <v>-4.889465037257364</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.82410521171722</v>
       </c>
       <c r="E99">
-        <v>-46.30343823109565</v>
+        <v>-47.59632888147055</v>
       </c>
       <c r="F99">
-        <v>0.3341309567131036</v>
+        <v>-0.1103743050987223</v>
       </c>
       <c r="G99">
-        <v>-4.257428925081866</v>
+        <v>-4.335511452171116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.35208211509873</v>
       </c>
       <c r="E100">
-        <v>-47.92808035879848</v>
+        <v>-50.43438014800267</v>
       </c>
       <c r="F100">
-        <v>-0.6810995648099144</v>
+        <v>-0.8949674608646908</v>
       </c>
       <c r="G100">
-        <v>-5.651675110582544</v>
+        <v>-4.401090048758539</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.86039303964636</v>
       </c>
       <c r="E101">
-        <v>-49.55695321334297</v>
+        <v>-52.76730617770469</v>
       </c>
       <c r="F101">
-        <v>-0.280358609622792</v>
+        <v>-1.026549480962378</v>
       </c>
       <c r="G101">
-        <v>-5.751021271670533</v>
+        <v>-4.735256515492573</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-20.41474558252946</v>
       </c>
       <c r="E102">
-        <v>-53.58236810044924</v>
+        <v>-54.60546019427667</v>
       </c>
       <c r="F102">
-        <v>-1.287221792010132</v>
+        <v>-1.190191804650615</v>
       </c>
       <c r="G102">
-        <v>-5.807651463665306</v>
+        <v>-5.131158035442936</v>
       </c>
     </row>
   </sheetData>
